--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_04_19_Cau.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -737,7 +737,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Loại record duplicate trước khi sum.</t>
+          <t>Sau khi deduplicate record trùng call_id với call 0,003 USD, chi phí task chỉ tính các unique calls: 0,002 + 0,005 + 0,003 = 0,01 USD.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -833,7 +833,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: User, Feature.</t>
+          <t>Để phân bổ chi phí và trả lời câu hỏi của CFO về mức tiêu hao ngân sách theo từng khách hàng, bản ghi telemetry bắt buộc phải gắn thẻ định danh khách hàng (`tenant_id`).</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
@@ -888,7 +888,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách population cố định trước release khỏi traffic thật sau release.</t>
+          <t>Phân biệt rạch ròi giữa offline eval và online eval: (a) Fixed benchmark trước release -&gt; offline eval; (b) Sample traffic thật sau release -&gt; online eval; (c) CI regression gate -&gt; offline eval; (d) Production drift/cohort monitoring -&gt; online eval.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính sample volume trước rồi nhân unit cost.</t>
+          <t>Chi phí eval hàng ngày: 1.000.000 requests * 1% sample rate * 0,002 USD/sampled request = 10.000 requests * 0,002 USD = 20 USD/ngày.</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1080,7 +1080,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Quality failure candidate, Feedback hoặc judge evidence.</t>
+          <t>Khi một trường hợp lỗi ở production có chứa dữ liệu nhạy cảm PII, quy trình đưa vào tập kiểm thử offline bắt buộc là phải làm sạch (sanitize/redact) dữ liệu PII và được chuyên gia thẩm định trước khi lưu trữ.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>60</v>
@@ -1128,7 +1128,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Judge identity/version, Score distribution.</t>
+          <t>Khi điểm số của LLM judge sụt giảm sau khi nâng cấp phiên bản nhưng độ đồng thuận của judge với nhãn chuyên gia cũng giảm, bước đầu tiên là phải kiểm tra sự lệch lạc của chính bộ đánh giá (evaluator drift).</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1272,7 +1272,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Personal-data flow, Processor/vendor.</t>
+          <t>Khi dữ liệu cá nhân của người dùng Việt Nam được chuyển ra máy chủ nước ngoài mà chưa rõ điều khoản xử lý dữ liệu và căn cứ pháp lý, hành động đúng là gắn cờ cảnh báo để đội ngũ pháp lý rà soát tuân thủ.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1423,7 +1423,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Span anomaly, Baseline comparison.</t>
+          <t>Dữ liệu trace cho thấy bước retrieval chậm nhưng chưa có thông tin về triển khai thay đổi hay kiểm chứng khắc phục; quan sát này mới chỉ cấu thành một giả thuyết nguyên nhân (cause candidate) chứ chưa phải kết luận gốc rễ.</t>
         </is>
       </c>
     </row>
